--- a/data/2.full_abstracting/26_02_01_full_decisions.xlsx
+++ b/data/2.full_abstracting/26_02_01_full_decisions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/2.full_abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2250" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A286E04C-6258-4559-B946-A6FF606713CD}"/>
+  <xr:revisionPtr revIDLastSave="2251" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D557F486-75B6-4FD6-A140-BCAEAE0C89FA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic_info" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="1521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1614" uniqueCount="1521">
   <si>
     <t>title</t>
   </si>
@@ -5065,9 +5065,12 @@
       <c r="B2" s="1" t="s">
         <v>113</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="D2" t="str">
         <f t="shared" ref="D2:D5" si="0">B2&amp;""&amp;C2</f>
-        <v>0095</v>
+        <v>0095a</v>
       </c>
       <c r="E2" t="s">
         <v>1490</v>

--- a/data/2.full_abstracting/26_02_01_full_decisions.xlsx
+++ b/data/2.full_abstracting/26_02_01_full_decisions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/2.full_abstracting/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2251" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D557F486-75B6-4FD6-A140-BCAEAE0C89FA}"/>
+  <xr:revisionPtr revIDLastSave="2254" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40461511-6882-4B27-8D29-058302B0BF8F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic_info" sheetId="1" r:id="rId1"/>
@@ -4515,15 +4515,6 @@
     <t>semicolumn-separated list of topics</t>
   </si>
   <si>
-    <t>10.1016/j.jrp.2026.104705</t>
-  </si>
-  <si>
-    <t>10.1177/08902070251409430</t>
-  </si>
-  <si>
-    <t>10.1007/s12187-025-10326-7</t>
-  </si>
-  <si>
     <t>Emotional Skills and Organizational Performance: A Buffering Effect of Personal Profiles</t>
   </si>
   <si>
@@ -4606,6 +4597,15 @@
   </si>
   <si>
     <t>Experiental features of volunteering predict changes in college students' social, emotional, and behavioral skills</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jrp.2026.104705</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1177/08902070251409430</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s12187-025-10326-7</t>
   </si>
 </sst>
 </file>
@@ -5072,23 +5072,23 @@
         <f t="shared" ref="D2:D5" si="0">B2&amp;""&amp;C2</f>
         <v>0095a</v>
       </c>
-      <c r="E2" t="s">
-        <v>1490</v>
+      <c r="E2" s="5" t="s">
+        <v>1518</v>
       </c>
       <c r="F2" t="s">
-        <v>1520</v>
+        <v>1517</v>
       </c>
       <c r="G2" t="s">
-        <v>1496</v>
+        <v>1493</v>
       </c>
       <c r="H2" t="s">
-        <v>1500</v>
+        <v>1497</v>
       </c>
       <c r="I2" t="s">
-        <v>1504</v>
+        <v>1501</v>
       </c>
       <c r="J2" t="s">
-        <v>1508</v>
+        <v>1505</v>
       </c>
       <c r="K2">
         <v>2026</v>
@@ -5100,13 +5100,13 @@
         <v>1455</v>
       </c>
       <c r="N2" t="s">
-        <v>1519</v>
+        <v>1516</v>
       </c>
       <c r="O2" t="s">
         <v>1486</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>1516</v>
+        <v>1513</v>
       </c>
       <c r="R2" t="s">
         <v>1162</v>
@@ -5115,10 +5115,10 @@
         <v>1404</v>
       </c>
       <c r="T2" t="s">
-        <v>1517</v>
+        <v>1514</v>
       </c>
       <c r="U2" t="s">
-        <v>1518</v>
+        <v>1515</v>
       </c>
       <c r="V2">
         <v>455</v>
@@ -5136,7 +5136,7 @@
         <v>1173</v>
       </c>
       <c r="AC2" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.35">
@@ -5151,19 +5151,19 @@
         <v>0096</v>
       </c>
       <c r="F3" t="s">
-        <v>1493</v>
+        <v>1490</v>
       </c>
       <c r="G3" t="s">
-        <v>1497</v>
+        <v>1494</v>
       </c>
       <c r="H3" t="s">
-        <v>1501</v>
+        <v>1498</v>
       </c>
       <c r="I3" t="s">
-        <v>1505</v>
+        <v>1502</v>
       </c>
       <c r="J3" t="s">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="K3">
         <v>2026</v>
@@ -5175,10 +5175,10 @@
         <v>1445</v>
       </c>
       <c r="AC3" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="AD3" t="s">
-        <v>1512</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.35">
@@ -5192,23 +5192,23 @@
         <f t="shared" si="0"/>
         <v>0097</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="5" t="s">
+        <v>1519</v>
+      </c>
+      <c r="F4" t="s">
         <v>1491</v>
       </c>
-      <c r="F4" t="s">
-        <v>1494</v>
-      </c>
       <c r="G4" t="s">
-        <v>1498</v>
+        <v>1495</v>
       </c>
       <c r="H4" t="s">
-        <v>1502</v>
+        <v>1499</v>
       </c>
       <c r="I4" t="s">
-        <v>1506</v>
+        <v>1503</v>
       </c>
       <c r="J4" t="s">
-        <v>1510</v>
+        <v>1507</v>
       </c>
       <c r="K4">
         <v>2026</v>
@@ -5220,10 +5220,10 @@
         <v>1445</v>
       </c>
       <c r="AC4" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="AD4" t="s">
-        <v>1513</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.35">
@@ -5237,23 +5237,23 @@
         <f t="shared" si="0"/>
         <v>0098</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="5" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F5" t="s">
         <v>1492</v>
       </c>
-      <c r="F5" t="s">
-        <v>1495</v>
-      </c>
       <c r="G5" t="s">
-        <v>1499</v>
+        <v>1496</v>
       </c>
       <c r="H5" t="s">
-        <v>1503</v>
+        <v>1500</v>
       </c>
       <c r="I5" t="s">
-        <v>1507</v>
+        <v>1504</v>
       </c>
       <c r="J5" t="s">
-        <v>1511</v>
+        <v>1508</v>
       </c>
       <c r="K5">
         <v>2026</v>
@@ -5265,10 +5265,10 @@
         <v>1445</v>
       </c>
       <c r="AC5" t="s">
-        <v>1514</v>
+        <v>1511</v>
       </c>
       <c r="AD5" t="s">
-        <v>1515</v>
+        <v>1512</v>
       </c>
     </row>
   </sheetData>
@@ -5282,9 +5282,12 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="Q2" r:id="rId1" xr:uid="{5966A0BA-F8BE-421F-8B6C-CFEFB9F7400D}"/>
+    <hyperlink ref="E2" r:id="rId2" xr:uid="{24F78708-FB91-4335-9D0C-93DC986F7A89}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{8A14DD5A-2F03-4D32-9D97-AAC9BD1F5702}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{22E0109C-EBC5-4BDF-AC36-7DC61EE9FB8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="14">
